--- a/zakresy.xlsx
+++ b/zakresy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ola4p\PycharmProjects\PythonProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C0A4062-543F-4DDC-802F-94BB796525E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61883D20-A7F6-43CF-A478-92CAE2298365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13755" yWindow="4770" windowWidth="17040" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6045" yWindow="5265" windowWidth="17040" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
   <si>
     <t>Pies</t>
   </si>
@@ -70,6 +70,9 @@
   </si>
   <si>
     <t>Zakres</t>
+  </si>
+  <si>
+    <t>Stosunek Sodu do Potasu</t>
   </si>
 </sst>
 </file>
@@ -120,10 +123,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -404,10 +406,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:K35"/>
+  <dimension ref="B2:L8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
@@ -438,8 +440,11 @@
       <c r="K2" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -470,8 +475,11 @@
       <c r="K3" s="1">
         <v>2.5</v>
       </c>
+      <c r="L3" s="1">
+        <v>27</v>
+      </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -502,8 +510,11 @@
       <c r="K4" s="1">
         <v>6.8</v>
       </c>
+      <c r="L4" s="1">
+        <v>40</v>
+      </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
@@ -534,8 +545,11 @@
       <c r="K5" s="1">
         <v>3</v>
       </c>
+      <c r="L5" s="1">
+        <v>32</v>
+      </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
@@ -566,8 +580,11 @@
       <c r="K6" s="1">
         <v>6.5</v>
       </c>
+      <c r="L6" s="1">
+        <v>41</v>
+      </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
@@ -598,8 +615,11 @@
       <c r="K7" s="1">
         <v>2</v>
       </c>
+      <c r="L7" s="1">
+        <v>30</v>
+      </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
@@ -630,180 +650,9 @@
       <c r="K8" s="1">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-    </row>
-    <row r="19" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-    </row>
-    <row r="21" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-    </row>
-    <row r="22" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-    </row>
-    <row r="23" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-    </row>
-    <row r="24" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="I24" s="2"/>
-    </row>
-    <row r="25" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="I25" s="2"/>
-    </row>
-    <row r="26" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="I26" s="2"/>
-    </row>
-    <row r="27" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="I27" s="2"/>
-    </row>
-    <row r="28" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="I28" s="2"/>
-    </row>
-    <row r="29" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-    </row>
-    <row r="30" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="I30" s="2"/>
-    </row>
-    <row r="31" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="I31" s="2"/>
-    </row>
-    <row r="32" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="I32" s="2"/>
-    </row>
-    <row r="33" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="I33" s="2"/>
-    </row>
-    <row r="34" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="I34" s="2"/>
-    </row>
-    <row r="35" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
+      <c r="L8" s="1">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
